--- a/docs/parameters.xlsx
+++ b/docs/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="153">
   <si>
     <t xml:space="preserve">DIGITAL TWIN PARAMETERS</t>
   </si>
@@ -393,9 +393,37 @@
     <t xml:space="preserve">Measurement threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">Minimum battery energy to start a measurement session 
-Calculated as: (mean_measurement_consumption - mean_solar_input) * max_duration + min battery = (14.23 - 3.615) * 10560/3600 + 15.264) = 46.40 Wh
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Minimum battery energy to start a measurement session 
+Calculated as: (mean_measurement_consumption - mean_solar_input) * max_duration + min battery = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">7.3666</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - 3.615) * 10560/3600 + 15.264) Wh
 (this simplification assumes that there is not data stored when the measurement window starts:  later, will be dynamically updated by checking data storage =&gt; might lower the measure threshold)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Mean consumption extracted from the "mean consumption" sheet 
@@ -458,27 +486,19 @@
     <t xml:space="preserve">Max battery energy (for charging) Alternative</t>
   </si>
   <si>
-    <t xml:space="preserve">Measurement threshold camer not Tof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum battery energy to start a measurement session 
-Calculated as: (mean_measurement_consumption - mean_solar_input) * max_duration + min battery = (7.25 - 3.615) * 600/3600 + 15.264) = 15.87 Wh
-(this simplification assumes that there is not data stored when the measurement window starts:  later, will be dynamically updated by checking data storage =&gt; might lower the measure threshold)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mean Consumption [W]</t>
   </si>
   <si>
-    <t xml:space="preserve">Source:</t>
+    <t xml:space="preserve">Values from</t>
   </si>
   <si>
     <t xml:space="preserve">Power Budget</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margins were taken from SE_DSD</t>
+    <t xml:space="preserve">Margins from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE_DSD</t>
   </si>
   <si>
     <t xml:space="preserve">Subsystem</t>
@@ -487,58 +507,52 @@
     <t xml:space="preserve">Margins</t>
   </si>
   <si>
-    <t xml:space="preserve">Operating Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADCS safe mode: Detumbling mode not considered since it is only during deployment</t>
+    <t xml:space="preserve">Operating Mode Nominal [Watt]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Mode with margins [watt]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDLE/CHARGING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEASUREMENT</t>
   </si>
   <si>
     <t xml:space="preserve">SAFE</t>
   </si>
   <si>
-    <t xml:space="preserve">CHARGING</t>
-  </si>
-  <si>
     <t xml:space="preserve">UHF-COM</t>
   </si>
   <si>
     <t xml:space="preserve">XBAND-COM</t>
   </si>
   <si>
-    <t xml:space="preserve">MEASUREMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UHF: always ON, either in uplink, downlink or beacon mode</t>
-  </si>
-  <si>
     <t xml:space="preserve">adcs</t>
   </si>
   <si>
-    <t xml:space="preserve">Values in Watt, margins included</t>
+    <t xml:space="preserve">novoviz camera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gnss</t>
   </si>
   <si>
     <t xml:space="preserve">obc</t>
   </si>
   <si>
-    <t xml:space="preserve">eps</t>
-  </si>
-  <si>
     <t xml:space="preserve">uhf</t>
   </si>
   <si>
     <t xml:space="preserve">x band</t>
   </si>
   <si>
-    <t xml:space="preserve">gnss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tof</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALL</t>
   </si>
   <si>
-    <t xml:space="preserve">camera</t>
+    <t xml:space="preserve">Note: ADCS safe mode: Detumbling mode not considered since it is only during deployment</t>
   </si>
   <si>
     <t xml:space="preserve">Data</t>
@@ -555,9 +569,6 @@
 =&gt; the TOF measure rate should be 800/(120*60) = 0.111 Mbps</t>
   </si>
   <si>
-    <t xml:space="preserve">SE_DSD</t>
-  </si>
-  <si>
     <t xml:space="preserve">GNSS data rate (generation)</t>
   </si>
   <si>
@@ -658,6 +669,12 @@
     <t xml:space="preserve">Attitude</t>
   </si>
   <si>
+    <t xml:space="preserve">Operating Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source:</t>
+  </si>
+  <si>
     <t xml:space="preserve">Y/Z Thomson spin</t>
   </si>
   <si>
@@ -668,6 +685,9 @@
   </si>
   <si>
     <t xml:space="preserve">Z+ towards sun + can rotate along Z axis *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARGING</t>
   </si>
   <si>
     <t xml:space="preserve">Nadir spin</t>
@@ -703,7 +723,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -817,6 +837,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="22"/>
       <color theme="5" tint="-0.5"/>
@@ -832,7 +858,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -859,18 +885,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.5999"/>
         <bgColor rgb="FFF7CAAC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="28">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1118,26 +1138,6 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin">
-        <color theme="6"/>
-      </right>
-      <top style="thin">
-        <color theme="6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right/>
       <top style="thin">
@@ -1202,7 +1202,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="79">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1411,26 +1411,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1439,52 +1435,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1499,7 +1455,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1507,11 +1463,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1531,11 +1487,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1555,11 +1511,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2424,12 +2380,13 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="92.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
         <v>57</v>
       </c>
       <c r="B8" s="46" t="n">
-        <v>46.4</v>
+        <f aca="false">(7.3666 - 3.615) * 10560/3600 + 15.264</f>
+        <v>26.2686933333333</v>
       </c>
       <c r="C8" s="46" t="s">
         <v>50</v>
@@ -2585,23 +2542,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="90.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="46" t="n">
-        <f aca="false">(7.25-3.615)*600/3600+15.264</f>
-        <v>15.8698333333333</v>
-      </c>
-      <c r="C18" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>59</v>
-      </c>
+    <row r="18" customFormat="false" ht="19.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0"/>
+      <c r="B18" s="0"/>
+      <c r="C18" s="0"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2626,23 +2572,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="10.55078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="13.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="11.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="14.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="5.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="11.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="6.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="64.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="9.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -2650,12 +2599,11 @@
       <c r="E1" s="40"/>
       <c r="F1" s="40"/>
       <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>82</v>
+      <c r="H1" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="53" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2666,358 +2614,526 @@
       <c r="E2" s="40"/>
       <c r="F2" s="40"/>
       <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="H2" s="52" t="s">
+        <v>81</v>
+      </c>
       <c r="I2" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="J2" s="54" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="55" t="s">
         <v>85</v>
-      </c>
-      <c r="B3" s="55" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="55" t="s">
-        <v>87</v>
       </c>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
       <c r="F3" s="55"/>
       <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56" t="s">
-        <v>88</v>
-      </c>
+      <c r="I3" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="55"/>
       <c r="B4" s="55"/>
-      <c r="C4" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="57" t="s">
+      <c r="C4" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="F4" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="G4" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="I4" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="K4" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="L4" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="M4" s="56" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="H4" s="57" t="s">
+      <c r="B5" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <f aca="false">C5*(1+B5)</f>
+        <v>1.596</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <f aca="false">D5*(1+B5)</f>
+        <v>1.596</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <f aca="false">E5*(1+B5)</f>
+        <v>1.596</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <f aca="false">F5*(1+B5)</f>
+        <v>1.596</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <f aca="false">G5*(1+B5)</f>
+        <v>1.596</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56" t="s">
+      <c r="B6" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <f aca="false">C6*(1+B6)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <f aca="false">D6*(1+B6)</f>
+        <v>1.01</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <f aca="false">E6*(1+B6)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <f aca="false">F6*(1+B6)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <f aca="false">G6*(1+B6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="56" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="57" t="s">
+      <c r="B7" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <f aca="false">C7*(1+B7)</f>
+        <v>0.24</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <f aca="false">D7*(1+B7)</f>
+        <v>0.24</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <f aca="false">E7*(1+B7)</f>
+        <v>0.24</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <f aca="false">F7*(1+B7)</f>
+        <v>0.24</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <f aca="false">G7*(1+B7)</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="58" t="n">
+      <c r="B8" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H8" s="54"/>
+      <c r="I8" s="1" t="n">
+        <f aca="false">C8*(1+B8)</f>
+        <v>0.6116</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <f aca="false">D8*(1+B8)</f>
+        <v>0.6116</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <f aca="false">E8*(1+B8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <f aca="false">F8*(1+B8)</f>
+        <v>0.6116</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <f aca="false">G8*(1+B8)</f>
+        <v>0.6116</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H9" s="54"/>
+      <c r="I9" s="1" t="n">
+        <f aca="false">C9*(1+B9)</f>
+        <v>1.704</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <f aca="false">D9*(1+B9)</f>
+        <v>1.704</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <f aca="false">E9*(1+B9)</f>
+        <v>1.704</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <f aca="false">F9*(1+B9)</f>
+        <v>1.704</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <f aca="false">G9*(1+B9)</f>
+        <v>1.704</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="C5" s="59" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D5" s="60" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E5" s="60" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F5" s="60" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G5" s="60" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H5" s="61" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="58" t="n">
+      <c r="C10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="54"/>
+      <c r="I10" s="1" t="n">
+        <f aca="false">C10*(1+B10)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <f aca="false">D10*(1+B10)</f>
+        <v>2.205</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <f aca="false">E10*(1+B10)</f>
+        <v>2.1</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <f aca="false">F10*(1+B10)</f>
+        <v>2.1</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <f aca="false">G10*(1+B10)</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="57" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="62" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D6" s="63" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E6" s="63" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F6" s="63" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G6" s="63" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H6" s="64" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="58" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C7" s="62" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="D7" s="63" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E7" s="63" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F7" s="63" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G7" s="63" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H7" s="64" t="n">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="57" t="s">
+      <c r="C11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H11" s="54"/>
+      <c r="I11" s="1" t="n">
+        <f aca="false">C11*(1+B11)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <f aca="false">D11*(1+B11)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <f aca="false">E11*(1+B11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <f aca="false">F11*(1+B11)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <f aca="false">G11*(1+B11)</f>
+        <v>17.64</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="58" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C8" s="62" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D8" s="63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E8" s="63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F8" s="63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G8" s="63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H8" s="64" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="57" t="s">
+      <c r="B12" s="58"/>
+      <c r="C12" s="1" t="n">
+        <f aca="false">SUM(C5:C11)</f>
+        <v>3.696</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <f aca="false">SUM(D5:D11)</f>
+        <v>6.806</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <f aca="false">SUM(E5:E11)</f>
+        <v>5.14</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <f aca="false">SUM(F5:F11)</f>
+        <v>5.696</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <f aca="false">SUM(G5:G11)</f>
+        <v>20.396</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <f aca="false">SUM(I5:I11)</f>
+        <v>4.1516</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <f aca="false">SUM(J5:J11)</f>
+        <v>7.3666</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <f aca="false">SUM(K5:K11)</f>
+        <v>5.64</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <f aca="false">SUM(L5:L11)</f>
+        <v>6.2516</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <f aca="false">SUM(M5:M11)</f>
+        <v>23.8916</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="H13" s="54"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="58" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="63" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="H9" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="65"/>
-      <c r="J9" s="65"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C10" s="62" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="D10" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="63" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="F10" s="63" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G10" s="63" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H10" s="64" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I10" s="65"/>
-      <c r="J10" s="65"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="57" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="64" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="I11" s="65"/>
-      <c r="J11" s="65"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="66" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="67" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="D12" s="68" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="E12" s="68" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="F12" s="68" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="G12" s="68" t="n">
-        <v>23.89</v>
-      </c>
-      <c r="H12" s="69" t="n">
-        <v>14.23</v>
-      </c>
-      <c r="I12" s="65"/>
-      <c r="J12" s="65"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" s="65"/>
-      <c r="C13" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="65"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65" t="n">
-        <f aca="false">14.23-(7.98-1)</f>
-        <v>7.25</v>
-      </c>
-      <c r="I14" s="65"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="70"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="70"/>
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="18.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:H2"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="A12:B12"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J1" r:id="rId1" display="Power Budget"/>
+    <hyperlink ref="I1" r:id="rId1" location="gid=640536346" display="Power Budget"/>
+    <hyperlink ref="I2" r:id="rId2" display="SE_DSD"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3046,7 +3162,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -3079,199 +3195,199 @@
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="71" t="n">
+        <v>102</v>
+      </c>
+      <c r="B4" s="60" t="n">
         <v>0.111</v>
       </c>
-      <c r="C4" s="72" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="73" t="s">
-        <v>82</v>
+      <c r="C4" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="62" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15"/>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
       <c r="E5" s="44" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="45" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B6" s="46" t="n">
         <v>0.0065</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="42" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>6.67E-005</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B8" s="46" t="n">
         <v>2097152</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="45" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B9" s="49" t="n">
         <v>0.0192</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B10" s="46" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D10" s="46"/>
       <c r="E10" s="51" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="45" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B11" s="46" t="n">
         <v>500</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E11" s="50"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B12" s="46" t="n">
         <v>10560</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="45" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B13" s="46" t="n">
         <v>1500</v>
       </c>
       <c r="C13" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>127</v>
-      </c>
       <c r="E13" s="51" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B14" s="46" t="n">
         <v>1860</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="45" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B15" s="46" t="n">
         <v>7200</v>
       </c>
       <c r="C15" s="46" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="45" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B16" s="46" t="n">
         <v>15</v>
@@ -3280,45 +3396,45 @@
         <v>35</v>
       </c>
       <c r="D16" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="E17" s="65" t="s">
         <v>133</v>
-      </c>
-      <c r="E16" s="50" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="74" t="s">
-        <v>135</v>
-      </c>
-      <c r="B17" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="75" t="s">
-        <v>136</v>
-      </c>
-      <c r="D17" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" s="76" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">200/60/10/1000</f>
         <v>0.000333333333333333</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3366,134 +3482,134 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="77" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
+      <c r="A1" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
     </row>
     <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="66" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+    </row>
+    <row r="3" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="70" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="71"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="69" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="70" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="78" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="79" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-    </row>
-    <row r="3" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="81" t="s">
+      <c r="C4" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="D4" s="67"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="81" t="s">
+      <c r="B5" s="70" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+    </row>
+    <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="69" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C6" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="78"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="80" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="81" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-    </row>
-    <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="80" t="s">
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B7" s="70" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C7" s="73" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="80" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="81" t="s">
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="B8" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="80" t="s">
+      <c r="C8" s="75" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="85" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="86" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" s="87"/>
+      <c r="D8" s="76"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="88" t="s">
-        <v>154</v>
+      <c r="D9" s="77" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="89"/>
+      <c r="D22" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="1">
